--- a/backend/templates/base/base_limites.xlsx
+++ b/backend/templates/base/base_limites.xlsx
@@ -35,7 +35,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,7 +80,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -97,6 +97,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -186,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -237,6 +243,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -246,14 +255,14 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1046,7 +1055,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>GOBIERNO REGIONAL CUSCO</t>
@@ -1060,28 +1069,28 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="12" customHeight="1">
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>SUB GERENCIA DE COBERTURA Y COMUNICACIONES</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="12" customHeight="1">
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>UNIDAD FUNCIONAL ESTUDIOS Y PROYECTOS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Laboratorio de Mecánica de Suelos, Materiales y Pavimentos</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="12" customHeight="1">
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t>«Año de la recuperación y consolidación de la economía peruana»</t>
@@ -1105,7 +1114,7 @@
       <c r="I8" s="7" t="n"/>
     </row>
     <row r="9" ht="6" customHeight="1"/>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>PROYECTO</t>
@@ -1120,7 +1129,7 @@
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>UBICACIÓN</t>
@@ -1151,7 +1160,7 @@
       </c>
       <c r="I11" s="10" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>SOLICITANTE</t>
@@ -1168,7 +1177,7 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>COORDENADAS</t>
@@ -1195,7 +1204,7 @@
       </c>
       <c r="I13" s="10" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>DATOS DE MUESTRA</t>
@@ -1243,149 +1252,149 @@
       <c r="I16" s="17" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Cod. Recipiente</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>N° de Golpes</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Peso del recipiente (g)</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Recip. + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Recip. + suelo seco (g)</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Peso agua (g)</t>
         </is>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="22">
         <f>IF(COUNT(B21:B22)=2,B21-B22,"")</f>
         <v/>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="22">
         <f>IF(COUNT(C21:C22)=2,C21-C22,"")</f>
         <v/>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="22">
         <f>IF(COUNT(D21:D22)=2,D21-D22,"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Peso suelo seco (g)</t>
         </is>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="22">
         <f>IF(COUNT(B20,B22)=2,B22-B20,"")</f>
         <v/>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="22">
         <f>IF(COUNT(C20,C22)=2,C22-C20,"")</f>
         <v/>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="22">
         <f>IF(COUNT(D20,D22)=2,D22-D20,"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>% de Humedad</t>
         </is>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="22">
         <f>IF(AND(ISNUMBER(B24),N(B24)&gt;0),IFERROR(B23/B24*100,0),"")</f>
         <v/>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="22">
         <f>IF(AND(ISNUMBER(C24),N(C24)&gt;0),IFERROR(C23/C24*100,0),"")</f>
         <v/>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="22">
         <f>IF(AND(ISNUMBER(D24),N(D24)&gt;0),IFERROR(D23/D24*100,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>LL Corregido (%)</t>
         </is>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="22">
         <f>IF(AND(ISNUMBER(B25),N(B19)&gt;0),B25*POWER(B19/25,0.121),"")</f>
         <v/>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="22">
         <f>IF(AND(ISNUMBER(C25),N(C19)&gt;0),C25*POWER(C19/25,0.121),"")</f>
         <v/>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="22">
         <f>IF(AND(ISNUMBER(D25),N(D19)&gt;0),D25*POWER(D19/25,0.121),"")</f>
         <v/>
       </c>
@@ -1396,7 +1405,7 @@
           <t>LÍMITE LÍQUIDO (L.L.)</t>
         </is>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="23">
         <f>IF(COUNTIF(B19:D19,25)&gt;0,INDEX(B25:D25,MATCH(25,B19:D19,0)),IF(COUNT(B26:D26)&gt;0,AVERAGE(B26:D26),0))</f>
         <v/>
       </c>
@@ -1421,99 +1430,99 @@
       <c r="I29" s="17" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Cod. Recipiente</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Peso del recipiente (g)</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n"/>
-      <c r="C32" s="20" t="n"/>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Recip. + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n"/>
-      <c r="C33" s="20" t="n"/>
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Recip. + suelo seco (g)</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n"/>
-      <c r="C34" s="20" t="n"/>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Peso agua (g)</t>
         </is>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="22">
         <f>IF(COUNT(B33:B34)=2,B33-B34,"")</f>
         <v/>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="22">
         <f>IF(COUNT(C33:C34)=2,C33-C34,"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Peso suelo seco (g)</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <f>IF(COUNT(B32,B34)=2,B34-B32,"")</f>
         <v/>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="22">
         <f>IF(COUNT(C32,C34)=2,C34-C32,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>% de Humedad</t>
         </is>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="22">
         <f>IF(AND(ISNUMBER(B36),N(B36)&gt;0),IFERROR(B35/B36*100,0),"")</f>
         <v/>
       </c>
-      <c r="C37" s="21">
+      <c r="C37" s="22">
         <f>IF(AND(ISNUMBER(C36),N(C36)&gt;0),IFERROR(C35/C36*100,0),"")</f>
         <v/>
       </c>
@@ -1524,7 +1533,7 @@
           <t>LÍMITE PLÁSTICO (L.P.)</t>
         </is>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="23">
         <f>IF(COUNT(B37:C37)&gt;0,AVERAGE(B37:C37),0)</f>
         <v/>
       </c>
@@ -1538,7 +1547,7 @@
           <t>ÍNDICE DE PLASTICIDAD (I.P.)</t>
         </is>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="23">
         <f>IF(AND(ISNUMBER(B27),ISNUMBER(B38)),B27-B38,"")</f>
         <v/>
       </c>
@@ -1547,13 +1556,13 @@
       <c r="E39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
       <c r="B40" s="7" t="n"/>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -1562,64 +1571,64 @@
       <c r="E40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>No plástico</t>
         </is>
       </c>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
+      <c r="D41" s="19" t="n"/>
+      <c r="E41" s="19" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>3 - 15</t>
         </is>
       </c>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>Ligeramente plástico</t>
         </is>
       </c>
-      <c r="D42" s="18" t="n"/>
-      <c r="E42" s="18" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>15 - 30</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>Baja plasticidad</t>
         </is>
       </c>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="19" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>&gt; 30</t>
         </is>
       </c>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>Alta plasticidad</t>
         </is>
       </c>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="19" t="n"/>
     </row>
     <row r="45" ht="6" customHeight="1"/>
     <row r="46">
@@ -1638,99 +1647,99 @@
       <c r="I46" s="17" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>Muestra 1</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>Muestra 2</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Cod. Cápsula</t>
         </is>
       </c>
-      <c r="B48" s="18" t="n"/>
-      <c r="C48" s="18" t="n"/>
+      <c r="B48" s="19" t="n"/>
+      <c r="C48" s="19" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Peso de cápsula (g)</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="21" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Cáps. + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B50" s="20" t="n"/>
-      <c r="C50" s="20" t="n"/>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="21" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Cáps. + suelo seco (g)</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="21" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Peso del agua (g)</t>
         </is>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="22">
         <f>IF(COUNT(B50:B51)=2,B50-B51,"")</f>
         <v/>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="22">
         <f>IF(COUNT(C50:C51)=2,C50-C51,"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Peso del suelo seco (g)</t>
         </is>
       </c>
-      <c r="B53" s="21">
+      <c r="B53" s="22">
         <f>IF(COUNT(B49,B51)=2,B51-B49,"")</f>
         <v/>
       </c>
-      <c r="C53" s="21">
+      <c r="C53" s="22">
         <f>IF(COUNT(C49,C51)=2,C51-C49,"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Contenido de humedad (%)</t>
         </is>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="22">
         <f>IF(AND(ISNUMBER(B53),N(B53)&gt;0),IFERROR(B52/B53*100,0),"")</f>
         <v/>
       </c>
-      <c r="C54" s="21">
+      <c r="C54" s="22">
         <f>IF(AND(ISNUMBER(C53),N(C53)&gt;0),IFERROR(C52/C53*100,0),"")</f>
         <v/>
       </c>
@@ -1741,7 +1750,7 @@
           <t>HUMEDAD NATURAL (w %)</t>
         </is>
       </c>
-      <c r="B55" s="22">
+      <c r="B55" s="23">
         <f>IF(COUNT(B54:C54)&gt;0,AVERAGE(B54:C54),0)</f>
         <v/>
       </c>
@@ -1766,28 +1775,28 @@
       <c r="I57" s="17" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="23" t="n"/>
-      <c r="B87" s="23" t="n"/>
-      <c r="C87" s="23" t="n"/>
-      <c r="D87" s="23" t="n"/>
-      <c r="E87" s="23" t="n"/>
-      <c r="F87" s="23" t="n"/>
-      <c r="G87" s="23" t="n"/>
-      <c r="H87" s="23" t="n"/>
-      <c r="I87" s="23" t="n"/>
+      <c r="A87" s="24" t="n"/>
+      <c r="B87" s="24" t="n"/>
+      <c r="C87" s="24" t="n"/>
+      <c r="D87" s="24" t="n"/>
+      <c r="E87" s="24" t="n"/>
+      <c r="F87" s="24" t="n"/>
+      <c r="G87" s="24" t="n"/>
+      <c r="H87" s="24" t="n"/>
+      <c r="I87" s="24" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="24" t="inlineStr">
+      <c r="A88" s="25" t="inlineStr">
         <is>
           <t>ESP. ENSAYOS GEOTECNICOS</t>
         </is>
       </c>
-      <c r="D88" s="24" t="inlineStr">
+      <c r="D88" s="25" t="inlineStr">
         <is>
           <t>ESP. SUELOS Y PAVIMENTOS</t>
         </is>
       </c>
-      <c r="G88" s="24" t="inlineStr">
+      <c r="G88" s="25" t="inlineStr">
         <is>
           <t>SUPERVISOR</t>
         </is>
@@ -1799,25 +1808,26 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C5:G5"/>
     <mergeCell ref="B55:E55"/>
+    <mergeCell ref="C3:G3"/>
     <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C4:G4"/>
     <mergeCell ref="A57:I57"/>
-    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C1:G1"/>
     <mergeCell ref="G88:I88"/>
-    <mergeCell ref="C5:F5"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C2:G2"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="D88:F88"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="C1:F1"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="C42:E42"/>
@@ -1828,7 +1838,6 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="C2:F2"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>

--- a/backend/templates/base/base_limites.xlsx
+++ b/backend/templates/base/base_limites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Reporte" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="_DATOS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="_GRAFICOS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="_MAPA" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DATOS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_GRAFICOS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_MAPA" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="FluidezGolpesX">'_DATOS'!$A$3:$A$5</definedName>
@@ -342,14 +342,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -370,7 +370,7 @@
             <v>Línea de Fluidez (Regresión)</v>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="DC2626"/>
               </a:solidFill>
@@ -380,7 +380,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -404,7 +404,7 @@
             <v>Puntos de Ensayo</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -413,10 +413,10 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E40AF"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="1E40AF"/>
                 </a:solidFill>
@@ -443,7 +443,7 @@
             <v>L.L. (25 golpes)</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -452,10 +452,10 @@
             <symbol val="circle"/>
             <size val="9"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="059669"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="059669"/>
                 </a:solidFill>
@@ -517,14 +517,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -545,7 +545,7 @@
             <v>Línea A</v>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="475569"/>
               </a:solidFill>
@@ -555,7 +555,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -579,7 +579,7 @@
             <v>Muestra</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -588,10 +588,10 @@
             <symbol val="circle"/>
             <size val="8"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="7C3AED"/>
                 </a:solidFill>
@@ -654,7 +654,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -669,9 +669,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -691,9 +691,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -713,13 +713,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -738,13 +738,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/backend/templates/base/base_limites.xlsx
+++ b/backend/templates/base/base_limites.xlsx
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,7 +221,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -237,6 +237,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1215,186 +1218,186 @@
           <t>Explor.:</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n"/>
+      <c r="C14" s="16" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Progresiva:</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n"/>
+      <c r="E14" s="16" t="n"/>
       <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Estrato:</t>
         </is>
       </c>
-      <c r="G14" s="10" t="n"/>
+      <c r="G14" s="16" t="n"/>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Lado:</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n"/>
+      <c r="I14" s="16" t="n"/>
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>DETERMINACIÓN DEL LÍMITE LÍQUIDO - MTC E 110</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="17" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Cod. Recipiente</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>N° de Golpes</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Peso del recipiente (g)</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Recip. + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Recip. + suelo seco (g)</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Peso agua (g)</t>
         </is>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="23">
         <f>IF(COUNT(B21:B22)=2,B21-B22,"")</f>
         <v/>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="23">
         <f>IF(COUNT(C21:C22)=2,C21-C22,"")</f>
         <v/>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <f>IF(COUNT(D21:D22)=2,D21-D22,"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Peso suelo seco (g)</t>
         </is>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="23">
         <f>IF(COUNT(B20,B22)=2,B22-B20,"")</f>
         <v/>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>IF(COUNT(C20,C22)=2,C22-C20,"")</f>
         <v/>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <f>IF(COUNT(D20,D22)=2,D22-D20,"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>% de Humedad</t>
         </is>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="23">
         <f>IF(AND(ISNUMBER(B24),N(B24)&gt;0),IFERROR(B23/B24*100,0),"")</f>
         <v/>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <f>IF(AND(ISNUMBER(C24),N(C24)&gt;0),IFERROR(C23/C24*100,0),"")</f>
         <v/>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <f>IF(AND(ISNUMBER(D24),N(D24)&gt;0),IFERROR(D23/D24*100,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>LL Corregido (%)</t>
         </is>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="23">
         <f>IF(AND(ISNUMBER(B25),N(B19)&gt;0),B25*POWER(B19/25,0.121),"")</f>
         <v/>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="23">
         <f>IF(AND(ISNUMBER(C25),N(C19)&gt;0),C25*POWER(C19/25,0.121),"")</f>
         <v/>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="23">
         <f>IF(AND(ISNUMBER(D25),N(D19)&gt;0),D25*POWER(D19/25,0.121),"")</f>
         <v/>
       </c>
@@ -1405,7 +1408,7 @@
           <t>LÍMITE LÍQUIDO (L.L.)</t>
         </is>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="24">
         <f>IF(COUNTIF(B19:D19,25)&gt;0,INDEX(B25:D25,MATCH(25,B19:D19,0)),IF(COUNT(B26:D26)&gt;0,AVERAGE(B26:D26),0))</f>
         <v/>
       </c>
@@ -1415,114 +1418,114 @@
     </row>
     <row r="28" ht="6" customHeight="1"/>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>DETERMINACIÓN DEL LÍMITE PLÁSTICO - MTC E 111</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="17" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Cod. Recipiente</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Peso del recipiente (g)</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n"/>
-      <c r="C32" s="21" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Recip. + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Recip. + suelo seco (g)</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Peso agua (g)</t>
         </is>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="23">
         <f>IF(COUNT(B33:B34)=2,B33-B34,"")</f>
         <v/>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="23">
         <f>IF(COUNT(C33:C34)=2,C33-C34,"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Peso suelo seco (g)</t>
         </is>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="23">
         <f>IF(COUNT(B32,B34)=2,B34-B32,"")</f>
         <v/>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="23">
         <f>IF(COUNT(C32,C34)=2,C34-C32,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>% de Humedad</t>
         </is>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="23">
         <f>IF(AND(ISNUMBER(B36),N(B36)&gt;0),IFERROR(B35/B36*100,0),"")</f>
         <v/>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="23">
         <f>IF(AND(ISNUMBER(C36),N(C36)&gt;0),IFERROR(C35/C36*100,0),"")</f>
         <v/>
       </c>
@@ -1533,7 +1536,7 @@
           <t>LÍMITE PLÁSTICO (L.P.)</t>
         </is>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="24">
         <f>IF(COUNT(B37:C37)&gt;0,AVERAGE(B37:C37),0)</f>
         <v/>
       </c>
@@ -1547,7 +1550,7 @@
           <t>ÍNDICE DE PLASTICIDAD (I.P.)</t>
         </is>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="24">
         <f>IF(AND(ISNUMBER(B27),ISNUMBER(B38)),B27-B38,"")</f>
         <v/>
       </c>
@@ -1556,13 +1559,13 @@
       <c r="E39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
       <c r="B40" s="7" t="n"/>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
@@ -1571,175 +1574,175 @@
       <c r="E40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>0 - 3</t>
         </is>
       </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>No plástico</t>
         </is>
       </c>
-      <c r="D41" s="19" t="n"/>
-      <c r="E41" s="19" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>3 - 15</t>
         </is>
       </c>
-      <c r="B42" s="19" t="n"/>
-      <c r="C42" s="19" t="inlineStr">
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="inlineStr">
         <is>
           <t>Ligeramente plástico</t>
         </is>
       </c>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>15 - 30</t>
         </is>
       </c>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="inlineStr">
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="inlineStr">
         <is>
           <t>Baja plasticidad</t>
         </is>
       </c>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>&gt; 30</t>
         </is>
       </c>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="19" t="inlineStr">
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>Alta plasticidad</t>
         </is>
       </c>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="19" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
     </row>
     <row r="45" ht="6" customHeight="1"/>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>ENSAYO DE HUMEDAD NATURAL - MTC E 108</t>
         </is>
       </c>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="17" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="F46" s="17" t="n"/>
-      <c r="G46" s="17" t="n"/>
-      <c r="H46" s="17" t="n"/>
-      <c r="I46" s="17" t="n"/>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="18" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="18" t="n"/>
+      <c r="H46" s="18" t="n"/>
+      <c r="I46" s="18" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>Muestra 1</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>Muestra 2</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Cod. Cápsula</t>
         </is>
       </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="19" t="n"/>
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="20" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Peso de cápsula (g)</t>
         </is>
       </c>
-      <c r="B49" s="21" t="n"/>
-      <c r="C49" s="21" t="n"/>
+      <c r="B49" s="22" t="n"/>
+      <c r="C49" s="22" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Cáps. + suelo húmedo (g)</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="21" t="n"/>
+      <c r="B50" s="22" t="n"/>
+      <c r="C50" s="22" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>Cáps. + suelo seco (g)</t>
         </is>
       </c>
-      <c r="B51" s="21" t="n"/>
-      <c r="C51" s="21" t="n"/>
+      <c r="B51" s="22" t="n"/>
+      <c r="C51" s="22" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Peso del agua (g)</t>
         </is>
       </c>
-      <c r="B52" s="22">
+      <c r="B52" s="23">
         <f>IF(COUNT(B50:B51)=2,B50-B51,"")</f>
         <v/>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="23">
         <f>IF(COUNT(C50:C51)=2,C50-C51,"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>Peso del suelo seco (g)</t>
         </is>
       </c>
-      <c r="B53" s="22">
+      <c r="B53" s="23">
         <f>IF(COUNT(B49,B51)=2,B51-B49,"")</f>
         <v/>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="23">
         <f>IF(COUNT(C49,C51)=2,C51-C49,"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>Contenido de humedad (%)</t>
         </is>
       </c>
-      <c r="B54" s="22">
+      <c r="B54" s="23">
         <f>IF(AND(ISNUMBER(B53),N(B53)&gt;0),IFERROR(B52/B53*100,0),"")</f>
         <v/>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="23">
         <f>IF(AND(ISNUMBER(C53),N(C53)&gt;0),IFERROR(C52/C53*100,0),"")</f>
         <v/>
       </c>
@@ -1750,7 +1753,7 @@
           <t>HUMEDAD NATURAL (w %)</t>
         </is>
       </c>
-      <c r="B55" s="23">
+      <c r="B55" s="24">
         <f>IF(COUNT(B54:C54)&gt;0,AVERAGE(B54:C54),0)</f>
         <v/>
       </c>
@@ -1760,43 +1763,43 @@
     </row>
     <row r="56" ht="6" customHeight="1"/>
     <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>GRÁFICOS DEL ENSAYO</t>
         </is>
       </c>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="17" t="n"/>
-      <c r="D57" s="17" t="n"/>
-      <c r="E57" s="17" t="n"/>
-      <c r="F57" s="17" t="n"/>
-      <c r="G57" s="17" t="n"/>
-      <c r="H57" s="17" t="n"/>
-      <c r="I57" s="17" t="n"/>
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="24" t="n"/>
-      <c r="B87" s="24" t="n"/>
-      <c r="C87" s="24" t="n"/>
-      <c r="D87" s="24" t="n"/>
-      <c r="E87" s="24" t="n"/>
-      <c r="F87" s="24" t="n"/>
-      <c r="G87" s="24" t="n"/>
-      <c r="H87" s="24" t="n"/>
-      <c r="I87" s="24" t="n"/>
+      <c r="A87" s="25" t="n"/>
+      <c r="B87" s="25" t="n"/>
+      <c r="C87" s="25" t="n"/>
+      <c r="D87" s="25" t="n"/>
+      <c r="E87" s="25" t="n"/>
+      <c r="F87" s="25" t="n"/>
+      <c r="G87" s="25" t="n"/>
+      <c r="H87" s="25" t="n"/>
+      <c r="I87" s="25" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="25" t="inlineStr">
+      <c r="A88" s="26" t="inlineStr">
         <is>
           <t>ESP. ENSAYOS GEOTECNICOS</t>
         </is>
       </c>
-      <c r="D88" s="25" t="inlineStr">
+      <c r="D88" s="26" t="inlineStr">
         <is>
           <t>ESP. SUELOS Y PAVIMENTOS</t>
         </is>
       </c>
-      <c r="G88" s="25" t="inlineStr">
+      <c r="G88" s="26" t="inlineStr">
         <is>
           <t>SUPERVISOR</t>
         </is>

--- a/backend/templates/base/base_limites.xlsx
+++ b/backend/templates/base/base_limites.xlsx
@@ -1248,11 +1248,6 @@
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="18" t="n"/>
       <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -1414,7 +1409,6 @@
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
     </row>
     <row r="28" ht="6" customHeight="1"/>
     <row r="29">
@@ -1425,12 +1419,6 @@
       </c>
       <c r="B29" s="18" t="n"/>
       <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="18" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -1541,8 +1529,6 @@
         <v/>
       </c>
       <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1555,8 +1541,6 @@
         <v/>
       </c>
       <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
@@ -1642,12 +1626,6 @@
       </c>
       <c r="B46" s="18" t="n"/>
       <c r="C46" s="18" t="n"/>
-      <c r="D46" s="18" t="n"/>
-      <c r="E46" s="18" t="n"/>
-      <c r="F46" s="18" t="n"/>
-      <c r="G46" s="18" t="n"/>
-      <c r="H46" s="18" t="n"/>
-      <c r="I46" s="18" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="19" t="inlineStr">
@@ -1758,8 +1736,6 @@
         <v/>
       </c>
       <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
     </row>
     <row r="56" ht="6" customHeight="1"/>
     <row r="57">
@@ -1812,36 +1788,36 @@
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="C3:G3"/>
     <mergeCell ref="C43:E43"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="G88:I88"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="D88:F88"/>
-    <mergeCell ref="B39:E39"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="C42:E42"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="B38:E38"/>
     <mergeCell ref="A88:C88"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/backend/templates/base/base_limites.xlsx
+++ b/backend/templates/base/base_limites.xlsx
@@ -161,7 +161,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -182,6 +182,50 @@
       <bottom style="thin">
         <color rgb="000F172A"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <top style="thin">
@@ -221,15 +265,14 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -237,9 +280,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -264,7 +304,7 @@
     <xf numFmtId="164" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1171,14 +1211,14 @@
       </c>
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Fecha Muestreo:</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -1218,25 +1258,25 @@
           <t>Explor.:</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n"/>
+      <c r="C14" s="11" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Progresiva:</t>
         </is>
       </c>
-      <c r="E14" s="16" t="n"/>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Estrato:</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n"/>
+      <c r="G14" s="11" t="n"/>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Lado:</t>
         </is>
       </c>
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="11" t="n"/>
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
